--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.49850382258626</v>
+        <v>6.743506871170267</v>
       </c>
       <c r="D2" t="n">
-        <v>41.71273427667246</v>
+        <v>6.778319319959275</v>
       </c>
       <c r="E2" t="n">
-        <v>2.79303687285822</v>
+        <v>0.4538684918394605</v>
       </c>
       <c r="F2" t="n">
-        <v>2.812964322359402</v>
+        <v>0.457106702383403</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.82969607435654</v>
+        <v>6.147325612082938</v>
       </c>
       <c r="D3" t="n">
-        <v>37.8004052681904</v>
+        <v>6.142565856080941</v>
       </c>
       <c r="E3" t="n">
-        <v>2.79303687285822</v>
+        <v>0.4538684918394605</v>
       </c>
       <c r="F3" t="n">
-        <v>2.812964322359402</v>
+        <v>0.457106702383403</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>44.66506332156788</v>
+        <v>7.25807278975478</v>
       </c>
       <c r="D4" t="n">
-        <v>44.6685671820341</v>
+        <v>7.258642167080542</v>
       </c>
       <c r="E4" t="n">
-        <v>2.79303687285822</v>
+        <v>0.4538684918394605</v>
       </c>
       <c r="F4" t="n">
-        <v>2.812964322359402</v>
+        <v>0.457106702383403</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
